--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iaros\Индивидуальный проект\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iaros\PycharmProjects\TestGenerator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA115B21-31B2-404C-9B0A-277B2DEB8C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0FFA1BE-4C97-4867-8ABE-1A9DAF98D4B9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>√2/2</t>
   </si>
@@ -110,29 +109,35 @@
     <t>A: 28;  B: 26;  C: 14;  D: 196</t>
   </si>
   <si>
-    <r>
-      <t>Найдите значение sin 45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>°</t>
-    </r>
-  </si>
-  <si>
     <t>A: -√3/2;  B: √2/2;  C: 0,5;  D: 1</t>
+  </si>
+  <si>
+    <t>Найдите значение sin 45°</t>
+  </si>
+  <si>
+    <t>Решите неравенство: x^2 + 5x + 6 &gt; 0</t>
+  </si>
+  <si>
+    <t>A: x ∈ (3, +∞);  B: x ∈ (2, 3);  C: x ∈ (-3, -2);  D: x ∈ (-∞, -3)</t>
+  </si>
+  <si>
+    <t>x ∈ (-3, -2)</t>
+  </si>
+  <si>
+    <t>Решите неравенство: sin x ≥ 0,5</t>
+  </si>
+  <si>
+    <t>x ∈ [π/6 + 2πn, 5π/6 + 2πn]</t>
+  </si>
+  <si>
+    <t>A: x ∈ [π/6 + 2πn, 5π/6 + 2πn];  B: x ∈ [-5π/6 + 2πn, -π/6 + 2πn];  C: x ∈ [-π/6 + 2πn, 5π/6 + 2πn];  D: x ∈ [-5π/6 + 2πn, -π/6 + 2πn]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3">
     <font>
       <sz val="16"/>
       <color theme="1"/>
@@ -149,8 +154,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Gilroy"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -176,8 +180,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -491,122 +495,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4CB67D-DDC5-4C05-BFDD-54A1BFFF4A60}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="38.07421875" customWidth="1"/>
-    <col min="3" max="3" width="28.53515625" customWidth="1"/>
+    <col min="1" max="1" width="38.08203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="105.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="1">
         <v>28</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>200</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -115,22 +115,22 @@
     <t>Найдите значение sin 45°</t>
   </si>
   <si>
-    <t>Решите неравенство: x^2 + 5x + 6 &gt; 0</t>
-  </si>
-  <si>
-    <t>A: x ∈ (3, +∞);  B: x ∈ (2, 3);  C: x ∈ (-3, -2);  D: x ∈ (-∞, -3)</t>
-  </si>
-  <si>
-    <t>x ∈ (-3, -2)</t>
-  </si>
-  <si>
     <t>Решите неравенство: sin x ≥ 0,5</t>
   </si>
   <si>
-    <t>x ∈ [π/6 + 2πn, 5π/6 + 2πn]</t>
-  </si>
-  <si>
-    <t>A: x ∈ [π/6 + 2πn, 5π/6 + 2πn];  B: x ∈ [-5π/6 + 2πn, -π/6 + 2πn];  C: x ∈ [-π/6 + 2πn, 5π/6 + 2πn];  D: x ∈ [-5π/6 + 2πn, -π/6 + 2πn]</t>
+    <t>Решите уравнение: x^2 + 5x + 6 = 0</t>
+  </si>
+  <si>
+    <t>2, 3</t>
+  </si>
+  <si>
+    <t>A: -2, -3;  B: 2, 3;  C: -2, 3;  D: 2, - 3</t>
+  </si>
+  <si>
+    <t>π/6, 5π/6</t>
+  </si>
+  <si>
+    <t>A: π/6, 5π/6;  B: 0;  C: -π/6, -5π/6;  D: π/4, 3π/4</t>
   </si>
 </sst>
 </file>
@@ -616,18 +616,18 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
